--- a/llvm-tryouts/LLM-Tests/outcomes.xlsx
+++ b/llvm-tryouts/LLM-Tests/outcomes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\simon\llm-llvm-adversarial\llvm-tryouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\simon\llm-llvm-adversarial\llvm-tryouts\LLM-Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5882B4-E35A-4C01-A02A-5113EAE16887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA3BC1D-198F-4F27-88E0-91529364A6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3190" windowWidth="25180" windowHeight="10490" activeTab="1" xr2:uid="{1509E5CE-4C87-4444-B404-E49071004A99}"/>
+    <workbookView xWindow="1000" yWindow="4000" windowWidth="17450" windowHeight="9470" activeTab="3" xr2:uid="{1509E5CE-4C87-4444-B404-E49071004A99}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle4" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="81">
   <si>
     <t>scsi_disk_emulate_start_stop.c</t>
   </si>
@@ -51,12 +51,6 @@
   </si>
   <si>
     <t>Run 3</t>
-  </si>
-  <si>
-    <t>Run 4</t>
-  </si>
-  <si>
-    <t>Run 5</t>
   </si>
   <si>
     <t>save</t>
@@ -287,6 +281,15 @@
   </si>
   <si>
     <t>Claude</t>
+  </si>
+  <si>
+    <t>subtle_overflow_orig.ll</t>
+  </si>
+  <si>
+    <t>subtle_overflow.c</t>
+  </si>
+  <si>
+    <t>subtle_overflow_obf.ll</t>
   </si>
 </sst>
 </file>
@@ -308,7 +311,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,6 +321,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -334,12 +343,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -685,34 +695,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="116" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -722,35 +732,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B9FD3E-9CEC-4873-A390-075EC7E33BC6}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="G1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="K1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="G1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="K1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -782,7 +793,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -790,532 +801,675 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="M5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L6" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="M6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L7" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="M7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L8" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="M8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L9" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="M9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="L10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="L11" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="L12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="L13" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="L14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K15" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="L15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L17" t="s">
+        <v>73</v>
+      </c>
+      <c r="M17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" t="s">
-        <v>75</v>
-      </c>
-      <c r="K16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L18" t="s">
+        <v>73</v>
+      </c>
+      <c r="M18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" t="s">
-        <v>75</v>
-      </c>
-      <c r="K17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s">
+        <v>73</v>
+      </c>
+      <c r="L20" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" t="s">
-        <v>75</v>
-      </c>
-      <c r="K18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s">
+        <v>73</v>
+      </c>
+      <c r="L22" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s">
-        <v>75</v>
-      </c>
-      <c r="K20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" t="s">
-        <v>75</v>
-      </c>
-      <c r="K21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-      <c r="G22" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s">
-        <v>75</v>
-      </c>
-      <c r="K22" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" t="s">
-        <v>75</v>
-      </c>
-      <c r="K23" t="s">
-        <v>75</v>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s">
+        <v>73</v>
+      </c>
+      <c r="L24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M24" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1331,392 +1485,1335 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE844ECE-D646-42E2-8DFF-D02DE93CF270}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="G1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="K1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s">
+        <v>74</v>
+      </c>
+      <c r="L15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s">
+        <v>73</v>
+      </c>
+      <c r="L21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" t="s">
-        <v>67</v>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s">
+        <v>73</v>
+      </c>
+      <c r="L24" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:M1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E9FEEC-E148-4CE6-BD45-C79C21ED42B9}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="G1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="K1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" t="s">
-        <v>48</v>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:M1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>